--- a/dist/static/excel/goods-template.xlsx
+++ b/dist/static/excel/goods-template.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29820" windowHeight="14840"/>
+    <workbookView windowHeight="15700"/>
   </bookViews>
   <sheets>
     <sheet name="商品导入" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">商品导入!$A$2:$M$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -26,91 +29,26 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>chenbaolong</author>
-  </authors>
-  <commentList>
-    <comment ref="B2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="0"/>
-          </rPr>
-          <t>必填项(*)
-字数不超过50</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">必填项(*)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="0"/>
-          </rPr>
-          <t>必填项(*)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">字数不超过500字符
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">请填写
-启用、停用
-未填写时默认为启用
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
-  <si>
-    <t>商品导入注意事项
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
+  <si>
+    <r>
+      <t>商品导入注意事项</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 1 商品名称、单位、批发价为必填项，商品编号确定商品的唯一性；
-2 若某商品只有一个单位则单位可不填，若某商品有多个单位，不填时默认为基础单位。
-3 单价不填默认为批发价，税率不填默认为销售税率。
-4 单价、折扣、折后单价之间的数值不对等时，系统会根据单价和折后单价帮您重新换算折扣。
-5 多属性商品请填写其具体单品的对应属性值，否则系统可能无法确定商品的唯一性。</t>
+2 单位一列同时填写换算关系：基础单位只写单位名（如：瓶），辅助单位写为「单位名(=换算数量基础单位)」（如：箱(=12瓶)，表示1箱=12瓶）；
+3 换算数量不得小于等于0；多单位时基础单位必须写在第一行；
+4 多规格商品每个规格的每个单位都要单独一行，规格型号与单位均需逐行填写，不得合并单元格；
+5 单价不填默认为批发价，税率不填默认为销售税率。</t>
+    </r>
   </si>
   <si>
     <t>商品编号</t>
@@ -125,62 +63,94 @@
     <t>单位</t>
   </si>
   <si>
+    <t>批发价</t>
+  </si>
+  <si>
+    <t>零售价</t>
+  </si>
+  <si>
+    <t>进货价</t>
+  </si>
+  <si>
+    <t>条码</t>
+  </si>
+  <si>
+    <t>库存数量</t>
+  </si>
+  <si>
     <t>分类</t>
   </si>
   <si>
     <t>品牌</t>
   </si>
   <si>
-    <t>批发价</t>
-  </si>
-  <si>
-    <t>零售价</t>
-  </si>
-  <si>
-    <t>进货价</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
     <t>状态</t>
   </si>
   <si>
-    <t>库存量</t>
-  </si>
-  <si>
-    <t>SP20230520</t>
-  </si>
-  <si>
-    <t>示例商品（导入时请删除）</t>
-  </si>
-  <si>
-    <t>500ml</t>
+    <t>SP0001</t>
+  </si>
+  <si>
+    <t>示例商品-多单位（导入时请删除）</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>瓶</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>箱(=12瓶)</t>
+  </si>
+  <si>
+    <t>SP0002</t>
+  </si>
+  <si>
+    <t>示例商品-多规格多单位（导入时请删除）</t>
+  </si>
+  <si>
+    <t>中号</t>
   </si>
   <si>
     <t>件</t>
   </si>
   <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>启用</t>
+    <t>箱(=20件)</t>
+  </si>
+  <si>
+    <t>大号</t>
+  </si>
+  <si>
+    <t>SP0003</t>
+  </si>
+  <si>
+    <t>示例商品-单单位（导入时请删除）</t>
+  </si>
+  <si>
+    <t>袋</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="28">
-    <font>
-      <sz val="11"/>
+  <fonts count="24">
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -188,41 +158,30 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <sz val="12"/>
+      <name val="SimSun Bold"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="黑体"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体-简"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -368,17 +327,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Verdana"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -389,7 +337,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,27 +528,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -702,21 +635,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -725,208 +667,132 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -976,9 +842,8 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="普通" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1309,306 +1174,375 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="15.6153846153846" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.7211538461538" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.9134615384615" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.6442307692308" style="2" customWidth="1"/>
-    <col min="6" max="7" width="16.2692307692308" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.2692307692308" style="3" customWidth="1"/>
-    <col min="9" max="10" width="17.2692307692308" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.9038461538462" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.5288461538462" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="14.8333333333333" customWidth="1"/>
+    <col min="2" max="2" width="34.2916666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.8666666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.8333333333333" customWidth="1"/>
+    <col min="5" max="7" width="12.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="15.0583333333333" customWidth="1"/>
+    <col min="10" max="13" width="12.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="112" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="2" customFormat="1" ht="19" customHeight="1" spans="1:13">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="M2" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" ht="19" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8" t="s">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+      <c r="G3">
+        <v>1.8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="13"/>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="13"/>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>21.6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="13"/>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="13"/>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>1900</v>
+      </c>
+      <c r="F6">
+        <v>2280</v>
+      </c>
+      <c r="G6">
+        <v>1710</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>300</v>
+      </c>
+      <c r="F7">
+        <v>360</v>
+      </c>
+      <c r="G7">
+        <v>270</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>5800</v>
+      </c>
+      <c r="F8">
+        <v>6960</v>
+      </c>
+      <c r="G8">
+        <v>5220</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9">
+        <v>50</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection password="FDEA" sheet="1" formatCells="0" insertRows="0" deleteRows="0" sort="0" objects="1"/>
-  <protectedRanges>
-    <protectedRange password="FDEA" sqref="J3:L3 A4:L1200 I3 A3:F3 H3 G3" name="区域2"/>
-  </protectedRanges>
+  <autoFilter ref="A2:M9">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <ignoredErrors>
+    <ignoredError sqref="B1:M1 A2:M8 A9:B9 E9:M9" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
-  <rangeList sheetStid="1" master="">
-    <arrUserId title="区域2" rangeCreator="" othersAccessPermission="edit"/>
-  </rangeList>
-</allowEditUser>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>